--- a/dati_plants.xlsx
+++ b/dati_plants.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -53,8 +53,11 @@
       <color theme="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +86,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+        <bgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -181,6 +190,8 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2702,7 +2713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="30.43" customWidth="1" style="15" min="1" max="1"/>
@@ -2726,42 +2737,42 @@
       </c>
       <c r="C1" s="17" t="inlineStr">
         <is>
-          <t>Vitalità</t>
+          <t>Vitalità (0-99)</t>
         </is>
       </c>
       <c r="D1" s="17" t="inlineStr">
         <is>
-          <t>Idratazione</t>
+          <t>Idratazione (0-99)</t>
         </is>
       </c>
       <c r="E1" s="17" t="inlineStr">
         <is>
-          <t>Res. Freddo</t>
+          <t>Res. Freddo (0-99)</t>
         </is>
       </c>
       <c r="F1" s="17" t="inlineStr">
         <is>
-          <t>Res. Caldo</t>
+          <t>Res. Caldo (0-99)</t>
         </is>
       </c>
       <c r="G1" s="17" t="inlineStr">
         <is>
-          <t>Res. Parassiti</t>
+          <t>Res. Parassiti (0-99)</t>
         </is>
       </c>
       <c r="H1" s="17" t="inlineStr">
         <is>
-          <t>Vegetazione</t>
+          <t>Vegetazione (0-99)</t>
         </is>
       </c>
       <c r="I1" s="17" t="inlineStr">
         <is>
-          <t>Metabolismo</t>
+          <t>Metabolismo (0-99)</t>
         </is>
       </c>
       <c r="J1" s="17" t="inlineStr">
         <is>
-          <t>Res. Vuoto</t>
+          <t>Res. Vuoto (0-99)</t>
         </is>
       </c>
     </row>
@@ -2776,45 +2787,29 @@
           <t>Seme base senza particolari proprietà</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F2" s="18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G2" s="18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H2" s="18" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="I2" s="18" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="J2" s="0" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
+      <c r="C2" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2825,48 +2820,32 @@
       </c>
       <c r="B3" s="18" t="inlineStr">
         <is>
-          <t>Piante robuste, alta vita ma lente</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>1.5x</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>1.1x</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
-      </c>
-      <c r="G3" s="18" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
-      </c>
-      <c r="H3" s="18" t="inlineStr">
-        <is>
-          <t>0.9x</t>
-        </is>
-      </c>
-      <c r="I3" s="18" t="inlineStr">
-        <is>
-          <t>0.8x</t>
-        </is>
-      </c>
-      <c r="J3" s="0" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
+          <t>Piante robuste, alta vita ma poco vegetative</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2877,48 +2856,32 @@
       </c>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t>Consuma metà acqua, soffre il caldo</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>0.5x</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
-      </c>
-      <c r="F4" s="19" t="inlineStr">
-        <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H4" s="18" t="inlineStr">
-        <is>
-          <t>1.2x</t>
-        </is>
-      </c>
-      <c r="I4" s="18" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="J4" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+          <t>Consuma poca acqua, cresce rigoglioso</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2929,48 +2892,32 @@
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>Resiste al gelo, vulnerabile al caldo</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>1.1x</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>0.85x</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>+65%</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>-30%</t>
-        </is>
-      </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>+15%</t>
-        </is>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>0.85x</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>0.85x</t>
-        </is>
-      </c>
-      <c r="J5" s="0" t="inlineStr">
-        <is>
-          <t>+25%</t>
-        </is>
+          <t>Resiste al gelo, consumo e crescita ridotti</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -2984,45 +2931,29 @@
           <t>Prospera nel caldo, molto assetato</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>1.1x</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>1.4x</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>-30%</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>+65%</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>+25%</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>0.8x</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>1.1x</t>
-        </is>
-      </c>
-      <c r="J6" s="0" t="inlineStr">
-        <is>
-          <t>+15%</t>
-        </is>
+      <c r="C6" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -3033,48 +2964,32 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>Immune ai parassiti, leggermente fragile</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>0.9x</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>+80%</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>1.1x</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="J7" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+          <t>Quasi immune ai parassiti, leggermente fragile</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3085,48 +3000,32 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Fogliame 1.7x, vulnerabile ai parassiti</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>0.95x</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>1.25x</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>-15%</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>1.7x</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="J8" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+          <t>Fogliame rigoglioso, assetato</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3137,48 +3036,32 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Metabolismo 1.6x, molto fragile e assetato</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>0.75x</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>1.5x</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>1.6x</t>
-        </is>
-      </c>
-      <c r="J9" s="0" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+          <t>Metabolismo alto, molto fragile e assetato</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3189,48 +3072,32 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>Equilibrato, bonus a tutto (Epico)</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>1.15x</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t>0.9x</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>+20%</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>+20%</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>+20%</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>1.1x</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t>0.9x</t>
-        </is>
-      </c>
-      <c r="J10" s="0" t="inlineStr">
-        <is>
-          <t>+15%</t>
-        </is>
+          <t>Equilibrato, bonus diffusi (Epico)</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -3244,45 +3111,29 @@
           <t>Adatto allo spazio, lento sulla Terra (Leggendario)</t>
         </is>
       </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t>0.6x</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>+45%</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>+30%</t>
-        </is>
-      </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>+35%</t>
-        </is>
-      </c>
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>0.7x</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="inlineStr">
-        <is>
-          <t>0.8x</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="inlineStr">
-        <is>
-          <t>+70%</t>
-        </is>
+      <c r="C11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -3866,24 +3717,261 @@
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="15"/>
-    <row r="50" ht="15.75" customHeight="1" s="15"/>
-    <row r="51" ht="15.75" customHeight="1" s="15"/>
-    <row r="52" ht="15.75" customHeight="1" s="15"/>
-    <row r="53" ht="15.75" customHeight="1" s="15"/>
-    <row r="54" ht="15.75" customHeight="1" s="15"/>
+    <row r="50" ht="15.75" customHeight="1" s="15">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>SCALA STATISTICHE SEMI (0-99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1" s="15">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>Baseline (neutro)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1" s="15">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Primarie (vitalita, vegetazione, metabolismo)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>10</v>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>99</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Moltiplicatore = stat / (10 + (stage-1)*0.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" s="15">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Primaria idratazione</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>10</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>99</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Come sopra; valore alto = più consumo acqua</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" s="15">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Resistenze (freddo, caldo, parassiti, vuoto)</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>99</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Frazione = clamp(stat / (100 + (stage-1)*1.0), 0, 0.95)</t>
+        </is>
+      </c>
+    </row>
     <row r="55" ht="15.75" customHeight="1" s="15"/>
-    <row r="56" ht="15.75" customHeight="1" s="15"/>
-    <row r="57" ht="15.75" customHeight="1" s="15"/>
-    <row r="58" ht="15.75" customHeight="1" s="15"/>
-    <row r="59" ht="15.75" customHeight="1" s="15"/>
-    <row r="60" ht="15.75" customHeight="1" s="15"/>
-    <row r="61" ht="15.75" customHeight="1" s="15"/>
-    <row r="62" ht="15.75" customHeight="1" s="15"/>
-    <row r="63" ht="15.75" customHeight="1" s="15"/>
+    <row r="56" ht="15.75" customHeight="1" s="15">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>REQUISITI PER STAGE (loop mondi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" s="15">
+      <c r="A57" s="21" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="inlineStr">
+        <is>
+          <t>Req. Primaria</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="inlineStr">
+        <is>
+          <t>Req. Resistenza</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1" s="15">
+      <c r="A58" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" t="n">
+        <v>100</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Baseline. Seme con stat 10 neutro</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1" s="15">
+      <c r="A59" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C59" t="n">
+        <v>104</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Stat 10 leggermente sottotono</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" s="15">
+      <c r="A60" t="n">
+        <v>10</v>
+      </c>
+      <c r="B60" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="C60" t="n">
+        <v>109</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Serve puntare a stat &gt;15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1" s="15">
+      <c r="A61" t="n">
+        <v>30</v>
+      </c>
+      <c r="B61" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="C61" t="n">
+        <v>129</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Semi base inutili. Necessari fusi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" s="15">
+      <c r="A62" t="n">
+        <v>50</v>
+      </c>
+      <c r="B62" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="C62" t="n">
+        <v>149</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Richiesto lategame</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" s="15">
+      <c r="A63" t="n">
+        <v>99</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="C63" t="n">
+        <v>198</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Endgame / Origine</t>
+        </is>
+      </c>
+    </row>
     <row r="64" ht="15.75" customHeight="1" s="15"/>
-    <row r="65" ht="15.75" customHeight="1" s="15"/>
-    <row r="66" ht="15.75" customHeight="1" s="15"/>
-    <row r="67" ht="15.75" customHeight="1" s="15"/>
+    <row r="65" ht="15.75" customHeight="1" s="15">
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t>MIGRAZIONE SAVE LEGACY</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" s="15">
+      <c r="A66" s="21" t="inlineStr">
+        <is>
+          <t>Euristica</t>
+        </is>
+      </c>
+      <c r="B66" s="21" t="inlineStr">
+        <is>
+          <t>Azione</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1" s="15">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>vitalita &lt; 3 nel save</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Primarie ×10, resistenze ×100. Idempotente. Applicata in GameSave.Load e Inventario.Load</t>
+        </is>
+      </c>
+    </row>
     <row r="68" ht="15.75" customHeight="1" s="15"/>
     <row r="69" ht="15.75" customHeight="1" s="15"/>
     <row r="70" ht="15.75" customHeight="1" s="15"/>
